--- a/Lopsided Productions (RIB) Risks-Issues-Bugs-Log.xlsx
+++ b/Lopsided Productions (RIB) Risks-Issues-Bugs-Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdigu\Desktop\Insomniac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD20B86-376F-407B-87E2-911B93CF25EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3908E269-835B-482E-B796-662BD2DC01AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E426D4A3-675A-4749-AD97-AF7CA7903CDF}"/>
+    <workbookView xWindow="28830" yWindow="900" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{E426D4A3-675A-4749-AD97-AF7CA7903CDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Risks" sheetId="3" r:id="rId1"/>
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="191">
   <si>
     <t>Lopsided Productions Issues Log</t>
   </si>
@@ -706,9 +706,6 @@
     <t>Lopsided Productions Bug Tracker</t>
   </si>
   <si>
-    <t>Last Update:  02/05/2026</t>
-  </si>
-  <si>
     <t>Bug Name</t>
   </si>
   <si>
@@ -763,6 +760,36 @@
   </si>
   <si>
     <t>J,N</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>BT003</t>
+  </si>
+  <si>
+    <t>Double Tap Speed</t>
+  </si>
+  <si>
+    <t>Fix (remove) the users ability to quikly double tap the flashlight to get rid of the monster quickly.</t>
+  </si>
+  <si>
+    <t>Last Update:  4/23/2026</t>
+  </si>
+  <si>
+    <t>BT004</t>
+  </si>
+  <si>
+    <t>Game Window</t>
+  </si>
+  <si>
+    <t>When game is open, the window cannot be resized.</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>May not be a design bug.</t>
   </si>
 </sst>
 </file>
@@ -1055,30 +1082,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1093,9 +1096,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
@@ -1117,6 +1117,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1125,6 +1152,28 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{8A8C821D-C0A4-4E8C-8E69-877CD3B7D532}"/>
   </cellStyles>
   <dxfs count="40">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1451,26 +1500,65 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
-        <patternFill>
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF92D050"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1747,67 +1835,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1822,58 +1849,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L25" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L25" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="B3:L25" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Risk Name" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Risk Description" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Risk Response Plan" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Risk Name" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Risk Description" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Risk Response Plan" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3CAF02DD-FC39-49C0-A216-15BB919FFAD5}" name="Table3" displayName="Table3" ref="B3:J33" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3CAF02DD-FC39-49C0-A216-15BB919FFAD5}" name="Table3" displayName="Table3" ref="B3:J33" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="B3:J33" xr:uid="{3CAF02DD-FC39-49C0-A216-15BB919FFAD5}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{01A5AB93-EACF-423C-A892-8152F12E0C58}" name="Ref #" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{463A199E-F90D-47D3-B981-56C66E690FAB}" name="Issue" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{B9C7834A-BAE0-4294-B124-EE37A0CF8EDA}" name="Owner" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{67553E0F-E2E3-408A-AD5B-32F4E0D78814}" name="Date Reported" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{05BD9C24-AA31-4CDF-9095-D2469DCBC911}" name="Due Date" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{CA385301-A356-4D83-A89A-B2A703722424}" name="Date Resolved" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{35975E18-3E12-4D66-AABB-325EE72065E5}" name="Status" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{663A80AC-A432-4346-A3D8-8ACCA140C3DB}" name="Comments" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{85FEE2AC-81AC-4356-B1C6-FDB89A573CCB}" name="Document Link" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{01A5AB93-EACF-423C-A892-8152F12E0C58}" name="Ref #" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{463A199E-F90D-47D3-B981-56C66E690FAB}" name="Issue" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{B9C7834A-BAE0-4294-B124-EE37A0CF8EDA}" name="Owner" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{67553E0F-E2E3-408A-AD5B-32F4E0D78814}" name="Date Reported" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{05BD9C24-AA31-4CDF-9095-D2469DCBC911}" name="Due Date" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{CA385301-A356-4D83-A89A-B2A703722424}" name="Date Resolved" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{35975E18-3E12-4D66-AABB-325EE72065E5}" name="Status" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{663A80AC-A432-4346-A3D8-8ACCA140C3DB}" name="Comments" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{85FEE2AC-81AC-4356-B1C6-FDB89A573CCB}" name="Document Link" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6946D23-8231-4BCF-8347-3A209AED2EC7}" name="Table2" displayName="Table2" ref="B3:L32" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6946D23-8231-4BCF-8347-3A209AED2EC7}" name="Table2" displayName="Table2" ref="B3:L32" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="B3:L32" xr:uid="{8502A7A6-495E-4A26-BA41-549614222EB5}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D1E70A13-85E0-4709-AC6A-FEE7A45EF7C2}" name="Ref #" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{9496C66F-F66B-43DC-BACC-1E500FB1A09E}" name="Bug Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FE0369B4-2E9E-468D-8D2E-817A2CAB6B10}" name="Bug Summary" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{CDBEA729-E814-4776-A49B-8F26574B171C}" name="Priotity_x000a_(High, Med, Low)" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{1B218A54-81A6-436F-9CAF-A7B1E3B1A24E}" name="Reported by" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{4E4037AC-072E-4C7C-85F7-6AC1D15BE4A4}" name="Date Reported" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{0A977F55-7674-4AA4-A2A9-6134163781DC}" name="Assigned to" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{15AA72AB-771C-4372-AD42-EBA4179C370D}" name="Date Due" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D2335B21-9980-4CF8-BDE7-350E325D2612}" name="Date Resolved" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{351CA830-4702-45BC-BFE7-C075F286B934}" name="Status_x000a_(Fixed, Broken, In-Progress)" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{6FBB8FE7-517A-4E14-B384-5A4841C7965D}" name="Comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D1E70A13-85E0-4709-AC6A-FEE7A45EF7C2}" name="Ref #" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{9496C66F-F66B-43DC-BACC-1E500FB1A09E}" name="Bug Name" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FE0369B4-2E9E-468D-8D2E-817A2CAB6B10}" name="Bug Summary" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{CDBEA729-E814-4776-A49B-8F26574B171C}" name="Priotity_x000a_(High, Med, Low)" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{1B218A54-81A6-436F-9CAF-A7B1E3B1A24E}" name="Reported by" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{4E4037AC-072E-4C7C-85F7-6AC1D15BE4A4}" name="Date Reported" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{0A977F55-7674-4AA4-A2A9-6134163781DC}" name="Assigned to" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{15AA72AB-771C-4372-AD42-EBA4179C370D}" name="Date Due" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{D2335B21-9980-4CF8-BDE7-350E325D2612}" name="Date Resolved" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{351CA830-4702-45BC-BFE7-C075F286B934}" name="Status_x000a_(Fixed, Broken, In-Progress)" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{6FBB8FE7-517A-4E14-B384-5A4841C7965D}" name="Comments" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2182,45 +2209,46 @@
   <dimension ref="B1:L26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
     <col min="3" max="3" width="27.140625" customWidth="1"/>
     <col min="4" max="4" width="36.85546875" customWidth="1"/>
     <col min="5" max="5" width="60.42578125" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="9" width="14.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" style="2" customWidth="1"/>
     <col min="12" max="12" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
     </row>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="19" t="s">
@@ -3080,14 +3108,14 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J25">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>101</formula>
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>101</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3117,11 +3145,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
@@ -3238,11 +3266,11 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -3370,10 +3398,10 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -3499,6 +3527,7 @@
   <dimension ref="B1:J33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="56.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
@@ -3511,30 +3540,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="2" spans="2:10" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="2:10" s="19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="36" t="s">
@@ -3922,499 +3951,537 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289371B6-92FB-4943-BA0F-5A389CF08052}">
   <sheetPr>
-    <tabColor theme="1"/>
+    <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="53"/>
-    <col min="2" max="2" width="10.5703125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="27" style="58" customWidth="1"/>
-    <col min="4" max="4" width="42.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="59" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="58" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="58" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="58" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="58" customWidth="1"/>
-    <col min="11" max="11" width="53.5703125" style="58" customWidth="1"/>
-    <col min="12" max="12" width="34.42578125" style="59" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="53"/>
+    <col min="1" max="1" width="2.7109375" style="44" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="49" customWidth="1"/>
+    <col min="3" max="3" width="27" style="49" customWidth="1"/>
+    <col min="4" max="4" width="42.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="50" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="49" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="49" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="49" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="49" customWidth="1"/>
+    <col min="11" max="11" width="53.5703125" style="49" customWidth="1"/>
+    <col min="12" max="12" width="34.42578125" style="50" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="44" t="s">
+    <row r="1" spans="2:12" s="37" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-    </row>
-    <row r="2" spans="2:12" s="47" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="46" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+    </row>
+    <row r="2" spans="2:12" s="39" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+    </row>
+    <row r="3" spans="2:12" s="41" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-    </row>
-    <row r="3" spans="2:12" s="49" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48" t="s">
+      <c r="D3" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="E3" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="F3" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="G3" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="48" t="s">
+      <c r="I3" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="J3" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="J3" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="48" t="s">
+      <c r="L3" s="40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B4" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="L3" s="48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" s="53" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B4" s="50" t="s">
+      <c r="C4" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="D4" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="E4" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="F4" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="G4" s="43">
+        <v>46128</v>
+      </c>
+      <c r="H4" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="G4" s="52">
+      <c r="I4" s="43">
+        <v>46135</v>
+      </c>
+      <c r="J4" s="43">
+        <v>46134</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="42"/>
+    </row>
+    <row r="5" spans="2:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="43">
         <v>46128</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="I5" s="43">
+        <v>46135</v>
+      </c>
+      <c r="J5" s="43">
+        <v>46134</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="42"/>
+    </row>
+    <row r="6" spans="2:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="43">
+        <v>46134</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="43">
+        <v>46142</v>
+      </c>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="L4" s="51"/>
-    </row>
-    <row r="5" spans="2:12" s="53" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B5" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="52">
-        <v>46128</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="52"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="L5" s="51"/>
-    </row>
-    <row r="6" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-    </row>
-    <row r="7" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
-    </row>
-    <row r="8" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="51"/>
-    </row>
-    <row r="9" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-    </row>
-    <row r="10" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-    </row>
-    <row r="11" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
-    </row>
-    <row r="12" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
-    </row>
-    <row r="13" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
-    </row>
-    <row r="14" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="51"/>
-    </row>
-    <row r="15" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="51"/>
-    </row>
-    <row r="16" spans="2:12" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="51"/>
-    </row>
-    <row r="17" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="55"/>
-    </row>
-    <row r="18" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="55"/>
-    </row>
-    <row r="19" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="55"/>
-    </row>
-    <row r="20" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
-    </row>
-    <row r="21" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
-    </row>
-    <row r="22" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-    </row>
-    <row r="23" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
-    </row>
-    <row r="24" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="55"/>
-    </row>
-    <row r="25" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="55"/>
-    </row>
-    <row r="26" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="55"/>
-    </row>
-    <row r="27" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="55"/>
-    </row>
-    <row r="28" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="55"/>
-    </row>
-    <row r="29" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="55"/>
-    </row>
-    <row r="31" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="55"/>
-    </row>
-    <row r="32" spans="2:12" s="57" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="55"/>
+      <c r="L6" s="42"/>
+    </row>
+    <row r="7" spans="2:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="43">
+        <v>46135</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="42"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="42"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="42"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="42"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="42"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="42"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="42"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="42"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="42"/>
+    </row>
+    <row r="17" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="46"/>
+    </row>
+    <row r="19" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="46"/>
+    </row>
+    <row r="20" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="46"/>
+    </row>
+    <row r="21" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="46"/>
+    </row>
+    <row r="22" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="46"/>
+    </row>
+    <row r="23" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="46"/>
+    </row>
+    <row r="24" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="46"/>
+    </row>
+    <row r="25" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="46"/>
+    </row>
+    <row r="26" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="46"/>
+    </row>
+    <row r="27" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="46"/>
+    </row>
+    <row r="28" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="46"/>
+    </row>
+    <row r="29" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="46"/>
+    </row>
+    <row r="30" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="46"/>
+    </row>
+    <row r="31" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="46"/>
+    </row>
+    <row r="32" spans="2:12" s="48" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
